--- a/04_DESIGN_TABLES/DesignTable_1603.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1603.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1115,24 +1120,74 @@
           <t>1603-02-02-02-FG</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.405</v>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>1603-02-02-02-FG</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1/8-27 (A1 (1) NPSM) x 1/8-27 (A1 (2) NPSM) x 1/8-27 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-02-02-02 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-02-02-02 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-02-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-02-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1143,6 +1198,11 @@
       <c r="W10" t="inlineStr">
         <is>
           <t>1603-02-02-02-FG</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1152,24 +1212,74 @@
           <t>1603-04-04-04-FG</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.54</v>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>1603-04-04-04-FG</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1/4-18 (A1 (1) NPSM) x 1/4-18 (A1 (2) NPSM) x 1/4-18 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-04-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-04-04-04 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1180,6 +1290,11 @@
       <c r="W11" t="inlineStr">
         <is>
           <t>1603-04-04-04-FG</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1189,24 +1304,74 @@
           <t>1603-06-06-06-FG</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.675</v>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>1603-06-06-06-FG</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3/8-18 (A1 (1) NPSM) x 3/8-18 (A1 (2) NPSM) x 3/8-18 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1217,6 +1382,11 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>1603-06-06-06-FG</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1263,24 +1433,74 @@
           <t>1603-12-12-12-FG</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.05</v>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>1603-12-12-12-FG</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3/4-14 (A1 (1) NPSM) x 3/4-14 (A1 (2) NPSM) x 3/4-14 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1291,6 +1511,11 @@
       <c r="W14" t="inlineStr">
         <is>
           <t>1603-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1300,24 +1525,74 @@
           <t>1603-16-16-16-FG</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.315</v>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>1603-16-16-16-FG</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1-11 1/2 (A1 (1) NPSM) x 1-11 1/2 (A1 (2) NPSM) x 1-11 1/2 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1328,6 +1603,11 @@
       <c r="W15" t="inlineStr">
         <is>
           <t>1603-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_1603.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1603.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1396,24 +1396,74 @@
           <t>1603-08-08-08-FG</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.84</v>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>1603-08-08-08-FG</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1/2-14 (A1 (1) NPSM) x 1/2-14 (A1 (2) NPSM) x 1/2-14 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1603-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); D1 / D2 bores measured on BRENNAN_1603-08-08-08-FG.stp 2026-10-20 (A14); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1603-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate) | 2026-10-20 A14: D1 / D2 bores 0.450 measured on the Brennan STEP (catalog prints the range 0.44/0.46); the other sizes = the Brennan TFA catalog p.48, all confirmed on the same STEP (nut faces 1.39, stem tips 1.11, nut hex 1.000, body flats 0.875) - staged, not shipped</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1424,6 +1474,11 @@
       <c r="W13" t="inlineStr">
         <is>
           <t>1603-08-08-08-FG</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
